--- a/artfynd/A 20829-2025 artfynd.xlsx
+++ b/artfynd/A 20829-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125570927</v>
+        <v>125572746</v>
       </c>
       <c r="B3" t="n">
-        <v>57793</v>
+        <v>97147</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,37 +813,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -851,17 +842,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkällegården, Stenkällegården, Vg</t>
+          <t>Dalen, Dalen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476284</v>
+        <v>476163</v>
       </c>
       <c r="R3" t="n">
-        <v>6504659</v>
+        <v>6504618</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,12 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre bohål i björkhögstubbe. Mycket lämplig sumpskogsmiljö.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125572746</v>
+        <v>125570927</v>
       </c>
       <c r="B4" t="n">
-        <v>97147</v>
+        <v>57793</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,28 +930,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -973,17 +968,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Vg</t>
+          <t>Stenkällegården, Stenkällegården, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476163</v>
+        <v>476284</v>
       </c>
       <c r="R4" t="n">
-        <v>6504618</v>
+        <v>6504659</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre bohål i björkhögstubbe. Mycket lämplig sumpskogsmiljö.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20829-2025 artfynd.xlsx
+++ b/artfynd/A 20829-2025 artfynd.xlsx
@@ -675,52 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125570741</v>
+        <v>125571003</v>
       </c>
       <c r="B2" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476270</v>
+        <v>476248</v>
       </c>
       <c r="R2" t="n">
-        <v>6504730</v>
+        <v>6504641</v>
       </c>
       <c r="S2" t="n">
         <v>30</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +790,7 @@
         <v>125572746</v>
       </c>
       <c r="B3" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125570927</v>
+        <v>125570741</v>
       </c>
       <c r="B4" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,14 +932,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -972,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476284</v>
+        <v>476270</v>
       </c>
       <c r="R4" t="n">
-        <v>6504659</v>
+        <v>6504730</v>
       </c>
       <c r="S4" t="n">
         <v>30</v>
@@ -1007,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre bohål i björkhögstubbe. Mycket lämplig sumpskogsmiljö.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,40 +1020,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125571003</v>
+        <v>125570927</v>
       </c>
       <c r="B5" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1094,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476248</v>
+        <v>476284</v>
       </c>
       <c r="R5" t="n">
-        <v>6504641</v>
+        <v>6504659</v>
       </c>
       <c r="S5" t="n">
         <v>30</v>
@@ -1129,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre bohål i björkhögstubbe. Mycket lämplig sumpskogsmiljö.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 20829-2025 artfynd.xlsx
+++ b/artfynd/A 20829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125571003</v>
       </c>
       <c r="B2" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,53 +787,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125572746</v>
+        <v>125570741</v>
       </c>
       <c r="B3" t="n">
-        <v>97202</v>
+        <v>57932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Vg</t>
+          <t>Stenkällegården, Stenkällegården, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476163</v>
+        <v>476270</v>
       </c>
       <c r="R3" t="n">
-        <v>6504618</v>
+        <v>6504730</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,62 +908,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125570741</v>
+        <v>125572746</v>
       </c>
       <c r="B4" t="n">
-        <v>57932</v>
+        <v>97209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenkällegården, Stenkällegården, Vg</t>
+          <t>Dalen, Dalen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476270</v>
+        <v>476163</v>
       </c>
       <c r="R4" t="n">
-        <v>6504730</v>
+        <v>6504618</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20829-2025 artfynd.xlsx
+++ b/artfynd/A 20829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125571003</v>
       </c>
       <c r="B2" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,62 +787,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125570741</v>
+        <v>125572746</v>
       </c>
       <c r="B3" t="n">
-        <v>57932</v>
+        <v>97212</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkällegården, Stenkällegården, Vg</t>
+          <t>Dalen, Dalen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476270</v>
+        <v>476163</v>
       </c>
       <c r="R3" t="n">
-        <v>6504730</v>
+        <v>6504618</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,53 +899,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125572746</v>
+        <v>125570741</v>
       </c>
       <c r="B4" t="n">
-        <v>97209</v>
+        <v>57933</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Vg</t>
+          <t>Stenkällegården, Stenkällegården, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476163</v>
+        <v>476270</v>
       </c>
       <c r="R4" t="n">
-        <v>6504618</v>
+        <v>6504730</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20829-2025 artfynd.xlsx
+++ b/artfynd/A 20829-2025 artfynd.xlsx
@@ -787,53 +787,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125572746</v>
+        <v>125570741</v>
       </c>
       <c r="B3" t="n">
-        <v>97212</v>
+        <v>57933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Vg</t>
+          <t>Stenkällegården, Stenkällegården, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476163</v>
+        <v>476270</v>
       </c>
       <c r="R3" t="n">
-        <v>6504618</v>
+        <v>6504730</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,62 +908,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125570741</v>
+        <v>125572746</v>
       </c>
       <c r="B4" t="n">
-        <v>57933</v>
+        <v>97212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenkällegården, Stenkällegården, Vg</t>
+          <t>Dalen, Dalen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476270</v>
+        <v>476163</v>
       </c>
       <c r="R4" t="n">
-        <v>6504730</v>
+        <v>6504618</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20829-2025 artfynd.xlsx
+++ b/artfynd/A 20829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125571003</v>
       </c>
       <c r="B2" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>125572746</v>
       </c>
       <c r="B4" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20829-2025 artfynd.xlsx
+++ b/artfynd/A 20829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125571003</v>
       </c>
       <c r="B2" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,62 +787,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125570741</v>
+        <v>125572746</v>
       </c>
       <c r="B3" t="n">
-        <v>57933</v>
+        <v>97217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkällegården, Stenkällegården, Vg</t>
+          <t>Dalen, Dalen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476270</v>
+        <v>476163</v>
       </c>
       <c r="R3" t="n">
-        <v>6504730</v>
+        <v>6504618</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,53 +899,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125572746</v>
+        <v>125570741</v>
       </c>
       <c r="B4" t="n">
-        <v>97216</v>
+        <v>57933</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Vg</t>
+          <t>Stenkällegården, Stenkällegården, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476163</v>
+        <v>476270</v>
       </c>
       <c r="R4" t="n">
-        <v>6504618</v>
+        <v>6504730</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20829-2025 artfynd.xlsx
+++ b/artfynd/A 20829-2025 artfynd.xlsx
@@ -787,53 +787,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125572746</v>
+        <v>125570741</v>
       </c>
       <c r="B3" t="n">
-        <v>97217</v>
+        <v>57933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Vg</t>
+          <t>Stenkällegården, Stenkällegården, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476163</v>
+        <v>476270</v>
       </c>
       <c r="R3" t="n">
-        <v>6504618</v>
+        <v>6504730</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,62 +908,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125570741</v>
+        <v>125572746</v>
       </c>
       <c r="B4" t="n">
-        <v>57933</v>
+        <v>97217</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenkällegården, Stenkällegården, Vg</t>
+          <t>Dalen, Dalen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476270</v>
+        <v>476163</v>
       </c>
       <c r="R4" t="n">
-        <v>6504730</v>
+        <v>6504618</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20829-2025 artfynd.xlsx
+++ b/artfynd/A 20829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125571003</v>
       </c>
       <c r="B2" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>125570741</v>
       </c>
       <c r="B3" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>125572746</v>
       </c>
       <c r="B4" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>125570927</v>
       </c>
       <c r="B5" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20829-2025 artfynd.xlsx
+++ b/artfynd/A 20829-2025 artfynd.xlsx
@@ -787,62 +787,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125570741</v>
+        <v>125572746</v>
       </c>
       <c r="B3" t="n">
-        <v>57934</v>
+        <v>97219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkällegården, Stenkällegården, Vg</t>
+          <t>Dalen, Dalen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476270</v>
+        <v>476163</v>
       </c>
       <c r="R3" t="n">
-        <v>6504730</v>
+        <v>6504618</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,53 +899,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125572746</v>
+        <v>125570741</v>
       </c>
       <c r="B4" t="n">
-        <v>97219</v>
+        <v>57934</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Vg</t>
+          <t>Stenkällegården, Stenkällegården, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476163</v>
+        <v>476270</v>
       </c>
       <c r="R4" t="n">
-        <v>6504618</v>
+        <v>6504730</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20829-2025 artfynd.xlsx
+++ b/artfynd/A 20829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125571003</v>
       </c>
       <c r="B2" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,53 +787,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125572746</v>
+        <v>125570741</v>
       </c>
       <c r="B3" t="n">
-        <v>97219</v>
+        <v>57934</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Vg</t>
+          <t>Stenkällegården, Stenkällegården, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476163</v>
+        <v>476270</v>
       </c>
       <c r="R3" t="n">
-        <v>6504618</v>
+        <v>6504730</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,62 +908,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125570741</v>
+        <v>125572746</v>
       </c>
       <c r="B4" t="n">
-        <v>57934</v>
+        <v>97221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenkällegården, Stenkällegården, Vg</t>
+          <t>Dalen, Dalen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476270</v>
+        <v>476163</v>
       </c>
       <c r="R4" t="n">
-        <v>6504730</v>
+        <v>6504618</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20829-2025 artfynd.xlsx
+++ b/artfynd/A 20829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125571003</v>
       </c>
       <c r="B2" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>125572746</v>
       </c>
       <c r="B4" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
